--- a/library/decompression/bfp8.xlsx
+++ b/library/decompression/bfp8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kele\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kele\Workspaces\hdl\library\decompression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE58ECE-4D9B-42D3-BDA0-0D18367DB82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A726B5-056B-4718-B2EB-7AB4F1DA3D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB36E99F-661D-4835-81D7-DB1D87AA1EF4}"/>
+    <workbookView xWindow="390" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{CB36E99F-661D-4835-81D7-DB1D87AA1EF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="6">
   <si>
     <t>exp</t>
   </si>
@@ -44,6 +44,15 @@
   </si>
   <si>
     <t>Q</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>Delay tlast</t>
   </si>
 </sst>
 </file>
@@ -59,7 +68,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +114,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -162,29 +177,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -501,37 +517,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2D90F0-9386-446E-90FF-89EDBBCBD6A2}">
-  <dimension ref="B3:U70"/>
+  <dimension ref="B3:V70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C3" s="5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B3" s="10"/>
+      <c r="C3" s="8">
         <v>63</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B4" s="6">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" s="8">
+        <v>63</v>
+      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" s="9">
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -540,42 +581,45 @@
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="10">
-        <v>0</v>
-      </c>
-      <c r="M4" s="10">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S4" s="1"/>
+      <c r="L4" s="11">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="V4" s="1"/>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -599,29 +643,32 @@
       <c r="J5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L5" s="11">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1"/>
+      <c r="L5" s="12">
+        <v>1</v>
+      </c>
+      <c r="M5" s="12">
+        <v>1</v>
+      </c>
+      <c r="N5" s="12">
+        <v>1</v>
+      </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
+      <c r="S5" s="1"/>
+      <c r="T5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" s="9">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -648,21 +695,22 @@
       <c r="J6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="O6" s="1"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B7" s="6">
+      <c r="V6" s="1"/>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -689,31 +737,34 @@
       <c r="J7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="10">
-        <v>2</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S7" s="1"/>
+      <c r="L7" s="11">
+        <v>2</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="6">
+      <c r="V7" s="1"/>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -740,29 +791,32 @@
       <c r="J8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="12">
         <v>3</v>
       </c>
-      <c r="M8" s="11">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1"/>
+      <c r="M8" s="12">
+        <v>1</v>
+      </c>
+      <c r="N8" s="12">
+        <v>1</v>
+      </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B9" s="6">
+      <c r="S8" s="1"/>
+      <c r="T8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -789,21 +843,22 @@
       <c r="J9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O9" s="1"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B10" s="6">
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -830,31 +885,34 @@
       <c r="J10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="11">
         <v>4</v>
       </c>
-      <c r="M10" s="10">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S10" s="1"/>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B11" s="6">
+      <c r="V10" s="1"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B11" s="9">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -881,29 +939,32 @@
       <c r="J11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="12">
         <v>5</v>
       </c>
-      <c r="M11" s="11">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1"/>
+      <c r="M11" s="12">
+        <v>1</v>
+      </c>
+      <c r="N11" s="12">
+        <v>1</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="S11" s="1"/>
+      <c r="T11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" s="9">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -930,21 +991,22 @@
       <c r="J12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O12" s="1"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="9">
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -971,33 +1033,36 @@
       <c r="J13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="11">
         <v>6</v>
       </c>
-      <c r="M13" s="10">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1"/>
-      <c r="O13" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T13" s="1"/>
+      <c r="M13" s="11">
+        <v>0</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="U13" s="1"/>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B14" s="6">
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="9">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1024,27 +1089,30 @@
       <c r="J14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="12">
         <v>7</v>
       </c>
-      <c r="M14" s="11">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1"/>
+      <c r="M14" s="12">
+        <v>1</v>
+      </c>
+      <c r="N14" s="12">
+        <v>1</v>
+      </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U14" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
+      <c r="T14" s="1"/>
+      <c r="U14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" s="9">
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1071,23 +1139,24 @@
       <c r="J15" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P15" s="1"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B16" s="6">
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1114,31 +1183,34 @@
       <c r="J16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="11">
         <v>8</v>
       </c>
-      <c r="M16" s="10">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1"/>
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
       <c r="O16" s="1"/>
-      <c r="P16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="6">
+      <c r="V16" s="1"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1165,27 +1237,30 @@
       <c r="J17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="12">
         <v>9</v>
       </c>
-      <c r="M17" s="11">
-        <v>1</v>
-      </c>
-      <c r="N17" s="1"/>
+      <c r="M17" s="12">
+        <v>1</v>
+      </c>
+      <c r="N17" s="12">
+        <v>1</v>
+      </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="6">
+      <c r="T17" s="1"/>
+      <c r="U17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B18" s="9">
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1212,23 +1287,24 @@
       <c r="J18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P18" s="1"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B19" s="9">
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1255,31 +1331,34 @@
       <c r="J19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="11">
         <v>10</v>
       </c>
-      <c r="M19" s="10">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1"/>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
+      <c r="N19" s="11">
+        <v>0</v>
+      </c>
       <c r="O19" s="1"/>
-      <c r="P19" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="U19" s="1"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B20" s="6">
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1306,27 +1385,30 @@
       <c r="J20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="12">
         <v>11</v>
       </c>
-      <c r="M20" s="11">
-        <v>1</v>
-      </c>
-      <c r="N20" s="1"/>
+      <c r="M20" s="12">
+        <v>1</v>
+      </c>
+      <c r="N20" s="12">
+        <v>1</v>
+      </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U20" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="6">
+      <c r="T20" s="1"/>
+      <c r="U20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" s="9">
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1353,23 +1435,24 @@
       <c r="J21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P21" s="1"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="6">
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B22" s="9">
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1396,33 +1479,36 @@
       <c r="J22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="11">
         <v>12</v>
       </c>
-      <c r="M22" s="10">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1"/>
+      <c r="M22" s="11">
+        <v>0</v>
+      </c>
+      <c r="N22" s="11">
+        <v>0</v>
+      </c>
       <c r="O22" s="1"/>
-      <c r="P22" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S22" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U22" s="1"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="P22" s="1"/>
+      <c r="Q22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B23" s="9">
         <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1449,25 +1535,28 @@
       <c r="J23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="13">
         <v>13</v>
       </c>
-      <c r="M23" s="12">
-        <v>1</v>
-      </c>
-      <c r="N23" s="1"/>
+      <c r="M23" s="13">
+        <v>1</v>
+      </c>
+      <c r="N23" s="13">
+        <v>1</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
-      <c r="U23" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B24" s="6">
+      <c r="U23" s="1"/>
+      <c r="V23" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B24" s="9">
         <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1494,25 +1583,26 @@
       <c r="J24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="1"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B25" s="6">
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B25" s="9">
         <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1539,31 +1629,34 @@
       <c r="J25" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="11">
         <v>14</v>
       </c>
-      <c r="M25" s="10">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1"/>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11">
+        <v>0</v>
+      </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U25" s="1"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="6">
+      <c r="Q25" s="1"/>
+      <c r="R25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B26" s="9">
         <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1590,25 +1683,28 @@
       <c r="J26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="13">
         <v>15</v>
       </c>
-      <c r="M26" s="12">
-        <v>1</v>
-      </c>
-      <c r="N26" s="1"/>
+      <c r="M26" s="13">
+        <v>1</v>
+      </c>
+      <c r="N26" s="13">
+        <v>1</v>
+      </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B27" s="6">
+      <c r="U26" s="1"/>
+      <c r="V26" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B27" s="9">
         <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -1635,25 +1731,26 @@
       <c r="J27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q27" s="1"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B28" s="6">
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B28" s="9">
         <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1680,924 +1777,1046 @@
       <c r="J28" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="11">
         <v>16</v>
       </c>
-      <c r="M28" s="10">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1"/>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
+      <c r="N28" s="11">
+        <v>0</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U28" s="1"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L29" s="12">
+      <c r="Q28" s="1"/>
+      <c r="R28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="L29" s="13">
         <v>17</v>
       </c>
-      <c r="M29" s="12">
-        <v>1</v>
-      </c>
-      <c r="N29" s="1"/>
+      <c r="M29" s="13">
+        <v>1</v>
+      </c>
+      <c r="N29" s="13">
+        <v>1</v>
+      </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L31" s="10">
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="L31" s="11">
         <v>18</v>
       </c>
-      <c r="M31" s="10">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1"/>
+      <c r="M31" s="11">
+        <v>0</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0</v>
+      </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-      <c r="Q31" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="R31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="L32" s="10">
+      <c r="Q31" s="1"/>
+      <c r="R31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U31" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="L32" s="11">
         <v>19</v>
       </c>
-      <c r="M32" s="10">
-        <v>1</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R32" s="1"/>
+      <c r="M32" s="11">
+        <v>1</v>
+      </c>
+      <c r="N32" s="11">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
-    </row>
-    <row r="33" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L33" s="10">
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L33" s="11">
         <v>20</v>
       </c>
-      <c r="M33" s="10">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1"/>
+      <c r="M33" s="11">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-      <c r="R33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L34" s="10">
+      <c r="R33" s="1"/>
+      <c r="S33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L34" s="11">
         <v>21</v>
       </c>
-      <c r="M34" s="10">
-        <v>1</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R34" s="1"/>
+      <c r="M34" s="11">
+        <v>1</v>
+      </c>
+      <c r="N34" s="11">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-    </row>
-    <row r="35" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L35" s="10">
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L35" s="11">
         <v>22</v>
       </c>
-      <c r="M35" s="10">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1"/>
+      <c r="M35" s="11">
+        <v>0</v>
+      </c>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-      <c r="R35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L36" s="10">
+      <c r="R35" s="1"/>
+      <c r="S35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L36" s="11">
         <v>23</v>
       </c>
-      <c r="M36" s="10">
-        <v>1</v>
-      </c>
-      <c r="N36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R36" s="1"/>
+      <c r="M36" s="11">
+        <v>1</v>
+      </c>
+      <c r="N36" s="11">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
-    </row>
-    <row r="37" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L37" s="12">
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L37" s="13">
         <v>24</v>
       </c>
-      <c r="M37" s="12">
-        <v>1</v>
-      </c>
-      <c r="N37" s="1"/>
+      <c r="M37" s="13">
+        <v>1</v>
+      </c>
+      <c r="N37" s="13">
+        <v>1</v>
+      </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U37" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O38" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V37" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
-    </row>
-    <row r="39" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L39" s="10">
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L39" s="11">
         <v>25</v>
       </c>
-      <c r="M39" s="10">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S39" s="1"/>
+      <c r="M39" s="11">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1"/>
+      <c r="P39" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R39" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
-    </row>
-    <row r="40" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L40" s="12">
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L40" s="13">
         <v>26</v>
       </c>
-      <c r="M40" s="12">
-        <v>1</v>
-      </c>
-      <c r="N40" s="1"/>
+      <c r="M40" s="13">
+        <v>1</v>
+      </c>
+      <c r="N40" s="13">
+        <v>1</v>
+      </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
-      <c r="S40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U40" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O41" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V40" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
-    </row>
-    <row r="42" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L42" s="10">
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L42" s="11">
         <v>27</v>
       </c>
-      <c r="M42" s="10">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S42" s="1"/>
+      <c r="M42" s="11">
+        <v>0</v>
+      </c>
+      <c r="N42" s="11">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1"/>
+      <c r="P42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
-    </row>
-    <row r="43" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L43" s="12">
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L43" s="13">
         <v>28</v>
       </c>
-      <c r="M43" s="12">
-        <v>1</v>
-      </c>
-      <c r="N43" s="1"/>
+      <c r="M43" s="13">
+        <v>1</v>
+      </c>
+      <c r="N43" s="13">
+        <v>1</v>
+      </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
-      <c r="S43" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U43" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O44" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V43" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
-    </row>
-    <row r="45" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L45" s="10">
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L45" s="11">
         <v>29</v>
       </c>
-      <c r="M45" s="10">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S45" s="1"/>
+      <c r="M45" s="11">
+        <v>0</v>
+      </c>
+      <c r="N45" s="11">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1"/>
+      <c r="P45" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
-    </row>
-    <row r="46" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L46" s="12">
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L46" s="13">
         <v>30</v>
       </c>
-      <c r="M46" s="12">
-        <v>1</v>
-      </c>
-      <c r="N46" s="1"/>
+      <c r="M46" s="13">
+        <v>1</v>
+      </c>
+      <c r="N46" s="13">
+        <v>1</v>
+      </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
-      <c r="S46" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="T46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P47" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-    </row>
-    <row r="48" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L48" s="10">
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L48" s="11">
         <v>31</v>
       </c>
-      <c r="M48" s="10">
-        <v>0</v>
-      </c>
-      <c r="N48" s="1"/>
+      <c r="M48" s="11">
+        <v>0</v>
+      </c>
+      <c r="N48" s="11">
+        <v>0</v>
+      </c>
       <c r="O48" s="1"/>
-      <c r="P48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="U48" s="1"/>
-    </row>
-    <row r="49" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L49" s="12">
+      <c r="V48" s="1"/>
+    </row>
+    <row r="49" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L49" s="13">
         <v>32</v>
       </c>
-      <c r="M49" s="12">
-        <v>1</v>
-      </c>
-      <c r="N49" s="1"/>
+      <c r="M49" s="13">
+        <v>1</v>
+      </c>
+      <c r="N49" s="13">
+        <v>1</v>
+      </c>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="T49" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P50" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
-    </row>
-    <row r="51" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L51" s="10">
+      <c r="V50" s="1"/>
+    </row>
+    <row r="51" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L51" s="11">
         <v>33</v>
       </c>
-      <c r="M51" s="10">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1"/>
+      <c r="M51" s="11">
+        <v>0</v>
+      </c>
+      <c r="N51" s="11">
+        <v>0</v>
+      </c>
       <c r="O51" s="1"/>
-      <c r="P51" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R51" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S51" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="U51" s="1"/>
-    </row>
-    <row r="52" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L52" s="12">
+      <c r="V51" s="1"/>
+    </row>
+    <row r="52" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L52" s="13">
         <v>34</v>
       </c>
-      <c r="M52" s="12">
-        <v>1</v>
-      </c>
-      <c r="N52" s="1"/>
+      <c r="M52" s="13">
+        <v>1</v>
+      </c>
+      <c r="N52" s="13">
+        <v>1</v>
+      </c>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="T52" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L53" s="13"/>
-      <c r="M53" s="13"/>
-      <c r="N53" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P53" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
-    </row>
-    <row r="54" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L54" s="10">
+      <c r="V53" s="1"/>
+    </row>
+    <row r="54" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L54" s="11">
         <v>35</v>
       </c>
-      <c r="M54" s="10">
-        <v>0</v>
-      </c>
-      <c r="N54" s="1"/>
+      <c r="M54" s="11">
+        <v>0</v>
+      </c>
+      <c r="N54" s="11">
+        <v>0</v>
+      </c>
       <c r="O54" s="1"/>
-      <c r="P54" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R54" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S54" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="U54" s="1"/>
-    </row>
-    <row r="55" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L55" s="12">
+      <c r="V54" s="1"/>
+    </row>
+    <row r="55" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L55" s="13">
         <v>36</v>
       </c>
-      <c r="M55" s="12">
-        <v>1</v>
-      </c>
-      <c r="N55" s="1"/>
+      <c r="M55" s="13">
+        <v>1</v>
+      </c>
+      <c r="N55" s="13">
+        <v>1</v>
+      </c>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-      <c r="T55" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="U55" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O56" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q56" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="V55" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
-    </row>
-    <row r="57" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L57" s="10">
+      <c r="V56" s="1"/>
+    </row>
+    <row r="57" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L57" s="11">
         <v>37</v>
       </c>
-      <c r="M57" s="10">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1"/>
+      <c r="M57" s="11">
+        <v>0</v>
+      </c>
+      <c r="N57" s="11">
+        <v>0</v>
+      </c>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
-      <c r="Q57" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S57" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U57" s="1"/>
-    </row>
-    <row r="58" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L58" s="12">
+      <c r="Q57" s="1"/>
+      <c r="R57" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T57" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V57" s="1"/>
+    </row>
+    <row r="58" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L58" s="13">
         <v>38</v>
       </c>
-      <c r="M58" s="12">
-        <v>1</v>
-      </c>
-      <c r="N58" s="1"/>
+      <c r="M58" s="13">
+        <v>1</v>
+      </c>
+      <c r="N58" s="13">
+        <v>1</v>
+      </c>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O59" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q59" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="7"/>
+      <c r="V58" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P59" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
-    </row>
-    <row r="60" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L60" s="10">
+      <c r="V59" s="1"/>
+    </row>
+    <row r="60" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L60" s="11">
         <v>39</v>
       </c>
-      <c r="M60" s="10">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1"/>
+      <c r="M60" s="11">
+        <v>0</v>
+      </c>
+      <c r="N60" s="11">
+        <v>0</v>
+      </c>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
-      <c r="Q60" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S60" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U60" s="1"/>
-    </row>
-    <row r="61" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L61" s="12">
+      <c r="Q60" s="1"/>
+      <c r="R60" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T60" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V60" s="1"/>
+    </row>
+    <row r="61" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L61" s="13">
         <v>40</v>
       </c>
-      <c r="M61" s="12">
-        <v>1</v>
-      </c>
-      <c r="N61" s="1"/>
+      <c r="M61" s="13">
+        <v>1</v>
+      </c>
+      <c r="N61" s="13">
+        <v>1</v>
+      </c>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O62" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q62" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P62" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
-    </row>
-    <row r="63" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L63" s="10">
+      <c r="V62" s="1"/>
+    </row>
+    <row r="63" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L63" s="11">
         <v>41</v>
       </c>
-      <c r="M63" s="10">
-        <v>0</v>
-      </c>
-      <c r="N63" s="1"/>
+      <c r="M63" s="11">
+        <v>0</v>
+      </c>
+      <c r="N63" s="11">
+        <v>0</v>
+      </c>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="Q63" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R63" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S63" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T63" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U63" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L64" s="10">
+      <c r="Q63" s="1"/>
+      <c r="R63" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T63" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V63" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L64" s="11">
         <v>42</v>
       </c>
-      <c r="M64" s="10">
-        <v>1</v>
-      </c>
-      <c r="N64" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P64" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R64" s="1"/>
+      <c r="M64" s="11">
+        <v>1</v>
+      </c>
+      <c r="N64" s="11">
+        <v>1</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
-    </row>
-    <row r="65" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L65" s="10">
+      <c r="V64" s="1"/>
+    </row>
+    <row r="65" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L65" s="11">
         <v>43</v>
       </c>
-      <c r="M65" s="10">
-        <v>0</v>
-      </c>
-      <c r="N65" s="1"/>
+      <c r="M65" s="11">
+        <v>0</v>
+      </c>
+      <c r="N65" s="11">
+        <v>0</v>
+      </c>
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
-      <c r="R65" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S65" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T65" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U65" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L66" s="10">
+      <c r="R65" s="1"/>
+      <c r="S65" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U65" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V65" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L66" s="11">
         <v>44</v>
       </c>
-      <c r="M66" s="10">
-        <v>1</v>
-      </c>
-      <c r="N66" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P66" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R66" s="1"/>
+      <c r="M66" s="11">
+        <v>1</v>
+      </c>
+      <c r="N66" s="11">
+        <v>1</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
-    </row>
-    <row r="67" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L67" s="10">
+      <c r="V66" s="1"/>
+    </row>
+    <row r="67" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L67" s="11">
         <v>45</v>
       </c>
-      <c r="M67" s="10">
-        <v>0</v>
-      </c>
-      <c r="N67" s="1"/>
+      <c r="M67" s="11">
+        <v>0</v>
+      </c>
+      <c r="N67" s="11">
+        <v>0</v>
+      </c>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
-      <c r="R67" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S67" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T67" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U67" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L68" s="10">
+      <c r="R67" s="1"/>
+      <c r="S67" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U67" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V67" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L68" s="11">
         <v>46</v>
       </c>
-      <c r="M68" s="10">
-        <v>1</v>
-      </c>
-      <c r="N68" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P68" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R68" s="1"/>
+      <c r="M68" s="11">
+        <v>1</v>
+      </c>
+      <c r="N68" s="11">
+        <v>1</v>
+      </c>
+      <c r="O68" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
-    </row>
-    <row r="69" spans="12:21" x14ac:dyDescent="0.25">
-      <c r="L69" s="10">
+      <c r="V68" s="1"/>
+    </row>
+    <row r="69" spans="12:22" x14ac:dyDescent="0.25">
+      <c r="L69" s="11">
         <v>47</v>
       </c>
-      <c r="M69" s="10">
-        <v>0</v>
-      </c>
-      <c r="N69" s="1"/>
+      <c r="M69" s="11">
+        <v>0</v>
+      </c>
+      <c r="N69" s="11">
+        <v>0</v>
+      </c>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
-      <c r="R69" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T69" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U69" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="R69" s="1"/>
+      <c r="S69" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U69" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V69" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="12:22" x14ac:dyDescent="0.25">
       <c r="M70">
         <f>SUM(M4:M69)</f>
         <v>25</v>
       </c>
+      <c r="N70">
+        <f>SUM(N4:N69)</f>
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="M61:M62"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="M43:M44"/>
-    <mergeCell ref="M46:M47"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="M52:M53"/>
-    <mergeCell ref="M55:M56"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="M29:M30"/>
+  <mergeCells count="54">
+    <mergeCell ref="N55:N56"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="N61:N62"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="N46:N47"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="N52:N53"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L20:L21"/>
     <mergeCell ref="M37:M38"/>
     <mergeCell ref="L61:L62"/>
     <mergeCell ref="M5:M6"/>
@@ -2614,13 +2833,19 @@
     <mergeCell ref="L26:L27"/>
     <mergeCell ref="L29:L30"/>
     <mergeCell ref="L37:L38"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="M61:M62"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="M55:M56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/library/decompression/bfp8.xlsx
+++ b/library/decompression/bfp8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kele\Workspaces\hdl\library\decompression\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\hdl\library\decompression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A726B5-056B-4718-B2EB-7AB4F1DA3D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F500C9-1B8E-4AEF-9AFE-6A56BC0736DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{CB36E99F-661D-4835-81D7-DB1D87AA1EF4}"/>
+    <workbookView xWindow="1260" yWindow="3405" windowWidth="22200" windowHeight="12180" xr2:uid="{CB36E99F-661D-4835-81D7-DB1D87AA1EF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -194,13 +194,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,13 +566,13 @@
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -581,7 +581,7 @@
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -619,7 +619,7 @@
       <c r="B5" s="9">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -643,27 +643,27 @@
       <c r="J5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L5" s="12">
-        <v>1</v>
-      </c>
-      <c r="M5" s="12">
-        <v>1</v>
-      </c>
-      <c r="N5" s="12">
-        <v>1</v>
+      <c r="L5" s="14">
+        <v>1</v>
+      </c>
+      <c r="M5" s="14">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="2" t="s">
+      <c r="T5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="U5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="V5" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -695,10 +695,10 @@
       <c r="J6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="6" t="s">
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="P6" s="1"/>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="O7" s="1"/>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="5" t="s">
         <v>1</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R7" s="5" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="3" t="s">
@@ -791,27 +791,27 @@
       <c r="J8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="14">
         <v>3</v>
       </c>
-      <c r="M8" s="12">
-        <v>1</v>
-      </c>
-      <c r="N8" s="12">
-        <v>1</v>
+      <c r="M8" s="14">
+        <v>1</v>
+      </c>
+      <c r="N8" s="14">
+        <v>0</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="5" t="s">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="V8" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -843,9 +843,9 @@
       <c r="J9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
       <c r="O9" s="3" t="s">
         <v>2</v>
       </c>
@@ -895,13 +895,13 @@
         <v>0</v>
       </c>
       <c r="O10" s="1"/>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="5" t="s">
         <v>1</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="R10" s="5" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="3" t="s">
@@ -939,27 +939,27 @@
       <c r="J11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="14">
         <v>5</v>
       </c>
-      <c r="M11" s="12">
-        <v>1</v>
-      </c>
-      <c r="N11" s="12">
-        <v>1</v>
+      <c r="M11" s="14">
+        <v>1</v>
+      </c>
+      <c r="N11" s="14">
+        <v>0</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="2" t="s">
+      <c r="T11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="V11" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -991,9 +991,9 @@
       <c r="J12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
       <c r="O12" s="3" t="s">
         <v>2</v>
       </c>
@@ -1089,14 +1089,14 @@
       <c r="J14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="14">
         <v>7</v>
       </c>
-      <c r="M14" s="12">
-        <v>1</v>
-      </c>
-      <c r="N14" s="12">
-        <v>1</v>
+      <c r="M14" s="14">
+        <v>1</v>
+      </c>
+      <c r="N14" s="14">
+        <v>0</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
@@ -1104,7 +1104,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="2" t="s">
+      <c r="U14" s="5" t="s">
         <v>1</v>
       </c>
       <c r="V14" s="6" t="s">
@@ -1139,10 +1139,10 @@
       <c r="J15" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="2" t="s">
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="5" t="s">
         <v>1</v>
       </c>
       <c r="P15" s="3" t="s">
@@ -1237,14 +1237,14 @@
       <c r="J17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="14">
         <v>9</v>
       </c>
-      <c r="M17" s="12">
-        <v>1</v>
-      </c>
-      <c r="N17" s="12">
-        <v>1</v>
+      <c r="M17" s="14">
+        <v>1</v>
+      </c>
+      <c r="N17" s="14">
+        <v>0</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1252,7 +1252,7 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="2" t="s">
+      <c r="U17" s="5" t="s">
         <v>1</v>
       </c>
       <c r="V17" s="6" t="s">
@@ -1287,10 +1287,10 @@
       <c r="J18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="2" t="s">
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="5" t="s">
         <v>1</v>
       </c>
       <c r="P18" s="3" t="s">
@@ -1385,14 +1385,14 @@
       <c r="J20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="14">
         <v>11</v>
       </c>
-      <c r="M20" s="12">
-        <v>1</v>
-      </c>
-      <c r="N20" s="12">
-        <v>1</v>
+      <c r="M20" s="14">
+        <v>1</v>
+      </c>
+      <c r="N20" s="14">
+        <v>0</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1400,7 +1400,7 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="2" t="s">
+      <c r="U20" s="5" t="s">
         <v>1</v>
       </c>
       <c r="V20" s="6" t="s">
@@ -1435,10 +1435,10 @@
       <c r="J21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="2" t="s">
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="5" t="s">
         <v>1</v>
       </c>
       <c r="P21" s="3" t="s">
@@ -1535,14 +1535,14 @@
       <c r="J23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="12">
         <v>13</v>
       </c>
-      <c r="M23" s="13">
-        <v>1</v>
-      </c>
-      <c r="N23" s="13">
-        <v>1</v>
+      <c r="M23" s="12">
+        <v>1</v>
+      </c>
+      <c r="N23" s="12">
+        <v>0</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -1551,7 +1551,7 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="2" t="s">
+      <c r="V23" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1583,9 +1583,9 @@
       <c r="J24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
       <c r="O24" s="3" t="s">
         <v>2</v>
       </c>
@@ -1683,14 +1683,14 @@
       <c r="J26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L26" s="13">
+      <c r="L26" s="12">
         <v>15</v>
       </c>
-      <c r="M26" s="13">
-        <v>1</v>
-      </c>
-      <c r="N26" s="13">
-        <v>1</v>
+      <c r="M26" s="12">
+        <v>1</v>
+      </c>
+      <c r="N26" s="12">
+        <v>0</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -1699,7 +1699,7 @@
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="2" t="s">
+      <c r="V26" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1731,9 +1731,9 @@
       <c r="J27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
       <c r="O27" s="3" t="s">
         <v>2</v>
       </c>
@@ -1804,14 +1804,14 @@
       <c r="V28" s="1"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="L29" s="13">
+      <c r="L29" s="12">
         <v>17</v>
       </c>
-      <c r="M29" s="13">
-        <v>1</v>
-      </c>
-      <c r="N29" s="13">
-        <v>1</v>
+      <c r="M29" s="12">
+        <v>1</v>
+      </c>
+      <c r="N29" s="12">
+        <v>0</v>
       </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -1820,14 +1820,14 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
-      <c r="V29" s="2" t="s">
+      <c r="V29" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
       <c r="O30" s="3" t="s">
         <v>2</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="N32" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="5" t="s">
         <v>1</v>
@@ -1934,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="N34" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="5" t="s">
         <v>1</v>
@@ -2008,14 +2008,14 @@
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L37" s="13">
+      <c r="L37" s="12">
         <v>24</v>
       </c>
-      <c r="M37" s="13">
-        <v>1</v>
-      </c>
-      <c r="N37" s="13">
-        <v>1</v>
+      <c r="M37" s="12">
+        <v>1</v>
+      </c>
+      <c r="N37" s="12">
+        <v>0</v>
       </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2035,9 +2035,9 @@
       </c>
     </row>
     <row r="38" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
       <c r="O38" s="3" t="s">
         <v>2</v>
       </c>
@@ -2077,14 +2077,14 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L40" s="13">
+      <c r="L40" s="12">
         <v>26</v>
       </c>
-      <c r="M40" s="13">
-        <v>1</v>
-      </c>
-      <c r="N40" s="13">
-        <v>1</v>
+      <c r="M40" s="12">
+        <v>1</v>
+      </c>
+      <c r="N40" s="12">
+        <v>0</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -2102,9 +2102,9 @@
       </c>
     </row>
     <row r="41" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
       <c r="O41" s="3" t="s">
         <v>2</v>
       </c>
@@ -2144,13 +2144,13 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L43" s="13">
+      <c r="L43" s="12">
         <v>28</v>
       </c>
-      <c r="M43" s="13">
-        <v>1</v>
-      </c>
-      <c r="N43" s="13">
+      <c r="M43" s="12">
+        <v>1</v>
+      </c>
+      <c r="N43" s="12">
         <v>1</v>
       </c>
       <c r="O43" s="1"/>
@@ -2169,9 +2169,9 @@
       </c>
     </row>
     <row r="44" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
       <c r="O44" s="3" t="s">
         <v>2</v>
       </c>
@@ -2211,14 +2211,14 @@
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L46" s="13">
+      <c r="L46" s="12">
         <v>30</v>
       </c>
-      <c r="M46" s="13">
-        <v>1</v>
-      </c>
-      <c r="N46" s="13">
-        <v>1</v>
+      <c r="M46" s="12">
+        <v>1</v>
+      </c>
+      <c r="N46" s="12">
+        <v>0</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -2236,9 +2236,9 @@
       </c>
     </row>
     <row r="47" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
       <c r="O47" s="5" t="s">
         <v>1</v>
       </c>
@@ -2280,14 +2280,14 @@
       <c r="V48" s="1"/>
     </row>
     <row r="49" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L49" s="13">
+      <c r="L49" s="12">
         <v>32</v>
       </c>
-      <c r="M49" s="13">
-        <v>1</v>
-      </c>
-      <c r="N49" s="13">
-        <v>1</v>
+      <c r="M49" s="12">
+        <v>1</v>
+      </c>
+      <c r="N49" s="12">
+        <v>0</v>
       </c>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -2303,9 +2303,9 @@
       </c>
     </row>
     <row r="50" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
       <c r="O50" s="5" t="s">
         <v>1</v>
       </c>
@@ -2347,13 +2347,13 @@
       <c r="V51" s="1"/>
     </row>
     <row r="52" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L52" s="13">
+      <c r="L52" s="12">
         <v>34</v>
       </c>
-      <c r="M52" s="13">
-        <v>1</v>
-      </c>
-      <c r="N52" s="13">
+      <c r="M52" s="12">
+        <v>1</v>
+      </c>
+      <c r="N52" s="12">
         <v>1</v>
       </c>
       <c r="O52" s="1"/>
@@ -2370,9 +2370,9 @@
       </c>
     </row>
     <row r="53" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
       <c r="O53" s="5" t="s">
         <v>1</v>
       </c>
@@ -2414,14 +2414,14 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L55" s="13">
+      <c r="L55" s="12">
         <v>36</v>
       </c>
-      <c r="M55" s="13">
-        <v>1</v>
-      </c>
-      <c r="N55" s="13">
-        <v>1</v>
+      <c r="M55" s="12">
+        <v>1</v>
+      </c>
+      <c r="N55" s="12">
+        <v>0</v>
       </c>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
@@ -2437,9 +2437,9 @@
       </c>
     </row>
     <row r="56" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
       <c r="O56" s="3" t="s">
         <v>2</v>
       </c>
@@ -2483,14 +2483,14 @@
       <c r="V57" s="1"/>
     </row>
     <row r="58" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L58" s="13">
+      <c r="L58" s="12">
         <v>38</v>
       </c>
-      <c r="M58" s="13">
-        <v>1</v>
-      </c>
-      <c r="N58" s="13">
-        <v>1</v>
+      <c r="M58" s="12">
+        <v>1</v>
+      </c>
+      <c r="N58" s="12">
+        <v>0</v>
       </c>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
@@ -2504,9 +2504,9 @@
       </c>
     </row>
     <row r="59" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
       <c r="O59" s="3" t="s">
         <v>2</v>
       </c>
@@ -2550,13 +2550,13 @@
       <c r="V60" s="1"/>
     </row>
     <row r="61" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L61" s="13">
+      <c r="L61" s="12">
         <v>40</v>
       </c>
-      <c r="M61" s="13">
-        <v>1</v>
-      </c>
-      <c r="N61" s="13">
+      <c r="M61" s="12">
+        <v>1</v>
+      </c>
+      <c r="N61" s="12">
         <v>1</v>
       </c>
       <c r="O61" s="1"/>
@@ -2571,9 +2571,9 @@
       </c>
     </row>
     <row r="62" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
       <c r="O62" s="3" t="s">
         <v>2</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="N64" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="5" t="s">
         <v>1</v>
@@ -2680,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="N66" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" s="5" t="s">
         <v>1</v>
@@ -2787,36 +2787,24 @@
       </c>
       <c r="N70">
         <f>SUM(N4:N69)</f>
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="N55:N56"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="N61:N62"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="N43:N44"/>
-    <mergeCell ref="N46:N47"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="N52:N53"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="M61:M62"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="M55:M56"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M29:M30"/>
     <mergeCell ref="M37:M38"/>
     <mergeCell ref="L61:L62"/>
     <mergeCell ref="M5:M6"/>
@@ -2833,19 +2821,31 @@
     <mergeCell ref="L26:L27"/>
     <mergeCell ref="L29:L30"/>
     <mergeCell ref="L37:L38"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="M61:M62"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="M43:M44"/>
-    <mergeCell ref="M46:M47"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="M52:M53"/>
-    <mergeCell ref="M55:M56"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N55:N56"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="N61:N62"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="N46:N47"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="N52:N53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
